--- a/MainTop/10.09.2026 Макс Озон/p2.xlsx
+++ b/MainTop/10.09.2026 Макс Озон/p2.xlsx
@@ -498,7 +498,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
